--- a/files/九龙-何文田-朗贤峰第IIA期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIA期.xlsx
@@ -8,9 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座 销控表" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座 销控表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座 销控表" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -44,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -113,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -178,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -194,51 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -623,7 +482,7 @@
     <row r="1" ht="40" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>朗贤峯第IIA期 - 一手销控汇总明细</t>
+          <t>朗贤峰第IIA期 - 一手销控汇总明细</t>
         </is>
       </c>
     </row>
@@ -2540,7 +2399,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -8606,7 +8465,7 @@
       </c>
       <c r="G167" s="3" t="inlineStr">
         <is>
-          <t>2024-04-28</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="H167" s="5" t="n">
@@ -18380,7 +18239,7 @@
       </c>
       <c r="G370" s="3" t="inlineStr">
         <is>
-          <t>2024-10-11</t>
+          <t>2024-10-30</t>
         </is>
       </c>
       <c r="H370" s="5" t="n">
@@ -20722,4361 +20581,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>朗贤峯第IIA期 - 1座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>128 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>44 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>58 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>26 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2540呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 2299呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr"/>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 2473呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 2299呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr"/>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-      <c r="H7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1431呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 1271呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 1333呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F8" s="17" t="inlineStr"/>
-      <c r="G8" s="17" t="inlineStr"/>
-      <c r="H8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1431呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 1271呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E9" s="18" t="inlineStr">
-        <is>
-          <t>D | 1333呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F9" s="17" t="inlineStr"/>
-      <c r="G9" s="17" t="inlineStr"/>
-      <c r="H9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1433呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>C | 1271呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 1333呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="17" t="inlineStr"/>
-      <c r="G10" s="17" t="inlineStr"/>
-      <c r="H10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1433呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>C | 1271呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 1333呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr"/>
-      <c r="G11" s="17" t="inlineStr"/>
-      <c r="H11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>B | 1433呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>C | 1271呎 (4+房)
-$3,503万
-$27,563/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>D | 1333呎 (4+房)
-$3,681万
-$27,617/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr"/>
-      <c r="G12" s="17" t="inlineStr"/>
-      <c r="H12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="18" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 1433呎 (4+房)
-$4,133万
-$28,841/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 1271呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>D | 1333呎 (4+房)
-$3,645万
-$27,344/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr"/>
-      <c r="G13" s="17" t="inlineStr"/>
-      <c r="H13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1433呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 1271呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 1333呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr"/>
-      <c r="G14" s="17" t="inlineStr"/>
-      <c r="H14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1433呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 1271呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 1333呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr"/>
-      <c r="G15" s="17" t="inlineStr"/>
-      <c r="H15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 1433呎 (4+房)
-$3,992万
-$27,856/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>C | 1271呎 (4+房)
-$3,377万
-$26,569/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>D | 1333呎 (4+房)
-$3,468万
-$26,015/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr"/>
-      <c r="G16" s="17" t="inlineStr"/>
-      <c r="H16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 1433呎 (4+房)
-$3,932万
-$27,441/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="inlineStr">
-        <is>
-          <t>C | 1271呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>D | 1333呎 (4+房)
-$3,503万
-$26,281/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr"/>
-      <c r="G17" s="17" t="inlineStr"/>
-      <c r="H17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 998呎 (3房)
-$2,477万
-$24,822/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 797呎 (3房)
-$1,991万
-$24,979/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="D18" s="18" t="inlineStr">
-        <is>
-          <t>C | 998呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>D | 685呎 (3房)
-$1,515万
-$22,118/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>E | 482呎 (2房)
-$1,073万
-$22,266/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G18" s="19" t="inlineStr">
-        <is>
-          <t>F | 482呎 (2房)
-$1,061万
-$22,012/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H18" s="19" t="inlineStr">
-        <is>
-          <t>G | 624呎 (2房)
-$1,339万
-$21,452/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 998呎 (3房)
-$2,528万
-$25,329/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 797呎 (3房)
-$1,986万
-$24,917/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>C | 998呎 (3房)
-$2,477万
-$24,818/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>D | 636呎 (2房)
-$1,404万
-$22,072/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>E | 482呎 (2房)
-$1,071万
-$22,212/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="inlineStr">
-        <is>
-          <t>F | 482呎 (2房)
-$1,052万
-$21,824/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
-        <is>
-          <t>G | 624呎 (2房)
-$1,628万
-$26,096/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 998呎 (3房)
-$2,478万
-$24,835/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="inlineStr">
-        <is>
-          <t>B | 797呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>C | 998呎 (3房)
-$2,514万
-$25,188/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>D | 636呎 (2房)
-$1,397万
-$21,964/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>E | 482呎 (2房)
-$1,065万
-$22,102/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>F | 482呎 (2房)
-$1,047万
-$21,716/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
-        <is>
-          <t>G | 624呎 (2房)
-$1,620万
-$25,968/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 998呎 (3房)
-$2,446万
-$24,512/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 797呎 (3房)
-$1,966万
-$24,670/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="D21" s="18" t="inlineStr">
-        <is>
-          <t>C | 998呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>D | 636呎 (2房)
-$1,390万
-$21,855/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>E | 482呎 (2房)
-$1,060万
-$21,992/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G21" s="19" t="inlineStr">
-        <is>
-          <t>F | 482呎 (2房)
-$1,042万
-$21,610/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
-        <is>
-          <t>G | 624呎 (2房)
-$1,612万
-$25,838/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 998呎 (3房)
-$2,435万
-$24,397/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 797呎 (3房)
-$1,996万
-$25,048/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="D22" s="18" t="inlineStr">
-        <is>
-          <t>C | 998呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>D | 636呎 (2房)
-$1,383万
-$21,747/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>E | 482呎 (2房)
-$1,055万
-$21,884/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>F | 482呎 (2房)
-$1,036万
-$21,502/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
-        <is>
-          <t>G | 624呎 (2房)
-$1,604万
-$25,712/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 998呎 (3房)
-$2,484万
-$24,888/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 797呎 (3房)
-$1,956万
-$24,547/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D23" s="18" t="inlineStr">
-        <is>
-          <t>C | 998呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E23" s="18" t="inlineStr">
-        <is>
-          <t>D | 636呎 (2房)
-$1,687万
-$26,520/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F23" s="18" t="inlineStr">
-        <is>
-          <t>E | 482呎 (2房)
-$1,286万
-$26,687/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G23" s="19" t="inlineStr">
-        <is>
-          <t>F | 482呎 (2房)
-$1,036万
-$21,502/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>G | 624呎 (2房)
-$1,604万
-$25,712/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 998呎 (3房)
-$2,410万
-$24,149/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="inlineStr">
-        <is>
-          <t>B | 797呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D24" s="18" t="inlineStr">
-        <is>
-          <t>C | 998呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E24" s="18" t="inlineStr">
-        <is>
-          <t>D | 636呎 (2房)
-$1,670万
-$26,259/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F24" s="18" t="inlineStr">
-        <is>
-          <t>E | 482呎 (2房)
-$1,274万
-$26,425/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G24" s="19" t="inlineStr">
-        <is>
-          <t>F | 482呎 (2房)
-$1,026万
-$21,290/呎
-(25年-01月)</t>
-        </is>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
-        <is>
-          <t>G | 624呎 (2房)
-$1,588万
-$25,457/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 998呎 (3房)
-$2,398万
-$24,030/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="inlineStr">
-        <is>
-          <t>B | 797呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D25" s="18" t="inlineStr">
-        <is>
-          <t>C | 998呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E25" s="18" t="inlineStr">
-        <is>
-          <t>D | 636呎 (2房)
-$1,662万
-$26,129/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F25" s="18" t="inlineStr">
-        <is>
-          <t>E | 482呎 (2房)
-$1,267万
-$26,295/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G25" s="18" t="inlineStr">
-        <is>
-          <t>F | 482呎 (2房)
-$1,245万
-$25,838/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>G | 624呎 (2房)
-$1,581万
-$25,332/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>A | 998呎 (3房)
-$2,386万
-$23,910/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="inlineStr">
-        <is>
-          <t>B | 797呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D26" s="18" t="inlineStr">
-        <is>
-          <t>C | 998呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E26" s="18" t="inlineStr">
-        <is>
-          <t>D | 636呎 (2房)
-$1,654万
-$26,002/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F26" s="18" t="inlineStr">
-        <is>
-          <t>E | 482呎 (2房)
-$1,261万
-$26,164/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G26" s="18" t="inlineStr">
-        <is>
-          <t>F | 482呎 (2房)
-$1,239万
-$25,707/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
-        <is>
-          <t>G | 624呎 (2房)
-$1,573万
-$25,207/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B27" s="18" t="inlineStr">
-        <is>
-          <t>A | 998呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="inlineStr">
-        <is>
-          <t>B | 797呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D27" s="18" t="inlineStr">
-        <is>
-          <t>C | 998呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 636呎 (2房)
-$1,646万
-$25,873/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 482呎 (2房)
-$1,255万
-$26,035/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 482呎 (2房)
-$1,233万
-$25,581/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>G | 624呎 (2房)
-$1,565万
-$25,082/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="inlineStr">
-        <is>
-          <t>A | 998呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="inlineStr">
-        <is>
-          <t>B | 797呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D28" s="18" t="inlineStr">
-        <is>
-          <t>C | 998呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 636呎 (2房)
-$1,637万
-$25,744/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 482呎 (2房)
-$1,249万
-$25,907/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 482呎 (2房)
-$1,227万
-$25,456/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>G | 624呎 (2房)
-$1,557万
-$24,958/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>A | 948呎 (3房)
-$2,666万
-$28,122/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="inlineStr">
-        <is>
-          <t>B | 754呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D29" s="18" t="inlineStr">
-        <is>
-          <t>C | 947呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 597呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 445呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 445呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 585呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>朗贤峯第IIA期 - 2座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>140 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>20 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>15 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>16 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>89 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2572呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1252呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 1249呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 2492呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 1505呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 994呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-      <c r="H7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 1429呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 1431呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>C | 926呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 568呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="18" t="inlineStr">
-        <is>
-          <t>E | 968呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G8" s="17" t="inlineStr"/>
-      <c r="H8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>A | 1429呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 1431呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>C | 926呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 568呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>E | 968呎 (3房)
-$2,551万
-$26,352/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="G9" s="17" t="inlineStr"/>
-      <c r="H9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 1431呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>C | 926呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E10" s="16" t="inlineStr">
-        <is>
-          <t>D | 568呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F10" s="18" t="inlineStr">
-        <is>
-          <t>E | 968呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G10" s="17" t="inlineStr"/>
-      <c r="H10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>B | 1431呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>C | 926呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="inlineStr">
-        <is>
-          <t>D | 568呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="inlineStr">
-        <is>
-          <t>E | 968呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G11" s="17" t="inlineStr"/>
-      <c r="H11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-$4,048万
-$28,267/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="inlineStr">
-        <is>
-          <t>B | 1431呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>C | 926呎 (3房)
-$2,402万
-$25,943/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="inlineStr">
-        <is>
-          <t>D | 568呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F12" s="19" t="inlineStr">
-        <is>
-          <t>E | 968呎 (3房)
-$2,530万
-$26,136/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G12" s="17" t="inlineStr"/>
-      <c r="H12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-$4,005万
-$27,968/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C13" s="18" t="inlineStr">
-        <is>
-          <t>B | 1431呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="inlineStr">
-        <is>
-          <t>C | 926呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="inlineStr">
-        <is>
-          <t>D | 568呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F13" s="19" t="inlineStr">
-        <is>
-          <t>E | 968呎 (3房)
-$2,452万
-$25,331/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G13" s="17" t="inlineStr"/>
-      <c r="H13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>B | 1431呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="inlineStr">
-        <is>
-          <t>C | 926呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E14" s="16" t="inlineStr">
-        <is>
-          <t>D | 568呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>E | 968呎 (3房)
-$2,530万
-$26,133/呎
-(24年-04月)</t>
-        </is>
-      </c>
-      <c r="G14" s="17" t="inlineStr"/>
-      <c r="H14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>B | 1431呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="inlineStr">
-        <is>
-          <t>C | 926呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E15" s="16" t="inlineStr">
-        <is>
-          <t>D | 568呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>E | 968呎 (3房)
-$2,427万
-$25,072/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G15" s="17" t="inlineStr"/>
-      <c r="H15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-$3,828万
-$26,732/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="C16" s="18" t="inlineStr">
-        <is>
-          <t>B | 1431呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="inlineStr">
-        <is>
-          <t>C | 926呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="E16" s="16" t="inlineStr">
-        <is>
-          <t>D | 568呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>E | 968呎 (3房)
-$2,428万
-$25,087/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="G16" s="17" t="inlineStr"/>
-      <c r="H16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="18" t="inlineStr">
-        <is>
-          <t>A | 1432呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="inlineStr">
-        <is>
-          <t>B | 1431呎 (4+房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>C | 926呎 (3房)
-$2,268万
-$24,492/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E17" s="16" t="inlineStr">
-        <is>
-          <t>D | 568呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F17" s="19" t="inlineStr">
-        <is>
-          <t>E | 968呎 (3房)
-$2,338万
-$24,153/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G17" s="17" t="inlineStr"/>
-      <c r="H17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>B | 796呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>C | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>D | 602呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G18" s="16" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
-        <is>
-          <t>G | 605呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="inlineStr">
-        <is>
-          <t>B | 796呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D19" s="16" t="inlineStr">
-        <is>
-          <t>C | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E19" s="16" t="inlineStr">
-        <is>
-          <t>D | 602呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F19" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G19" s="16" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
-        <is>
-          <t>G | 605呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>B | 796呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="inlineStr">
-        <is>
-          <t>C | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E20" s="16" t="inlineStr">
-        <is>
-          <t>D | 602呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F20" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G20" s="16" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>G | 605呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C21" s="16" t="inlineStr">
-        <is>
-          <t>B | 796呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>C | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="inlineStr">
-        <is>
-          <t>D | 602呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F21" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G21" s="16" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>G | 605呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C22" s="16" t="inlineStr">
-        <is>
-          <t>B | 796呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>C | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="inlineStr">
-        <is>
-          <t>D | 602呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F22" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G22" s="16" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
-        <is>
-          <t>G | 605呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C23" s="16" t="inlineStr">
-        <is>
-          <t>B | 796呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>C | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="inlineStr">
-        <is>
-          <t>D | 602呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F23" s="16" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G23" s="16" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
-        <is>
-          <t>G | 605呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C24" s="16" t="inlineStr">
-        <is>
-          <t>B | 796呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>C | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="inlineStr">
-        <is>
-          <t>D | 602呎 (2房)
-$1,521万
-$25,271/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F24" s="20" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$1,261万
-$25,733/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G24" s="20" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$1,250万
-$25,500/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H24" s="20" t="inlineStr">
-        <is>
-          <t>G | 605呎 (2房)
-$1,513万
-$25,003/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C25" s="16" t="inlineStr">
-        <is>
-          <t>B | 796呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>C | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="inlineStr">
-        <is>
-          <t>D | 602呎 (2房)
-$1,514万
-$25,146/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F25" s="20" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$1,255万
-$25,604/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$1,243万
-$25,376/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>G | 605呎 (2房)
-$1,505万
-$24,879/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C26" s="16" t="inlineStr">
-        <is>
-          <t>B | 796呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>C | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="inlineStr">
-        <is>
-          <t>D | 602呎 (2房)
-$1,463万
-$24,301/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F26" s="20" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$1,248万
-$25,478/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G26" s="20" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$1,237万
-$25,251/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H26" s="20" t="inlineStr">
-        <is>
-          <t>G | 605呎 (2房)
-$1,498万
-$24,757/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B27" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C27" s="16" t="inlineStr">
-        <is>
-          <t>B | 796呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>C | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="inlineStr">
-        <is>
-          <t>D | 602呎 (2房)
-$1,456万
-$24,181/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F27" s="20" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$1,242万
-$25,353/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G27" s="20" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$1,231万
-$25,127/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H27" s="20" t="inlineStr">
-        <is>
-          <t>G | 605呎 (2房)
-$1,490万
-$24,635/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B28" s="16" t="inlineStr">
-        <is>
-          <t>A | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C28" s="16" t="inlineStr">
-        <is>
-          <t>B | 796呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>C | 997呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="inlineStr">
-        <is>
-          <t>D | 602呎 (2房)
-$1,448万
-$24,061/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F28" s="20" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$1,236万
-$25,227/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="G28" s="20" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$1,225万
-$25,002/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="H28" s="20" t="inlineStr">
-        <is>
-          <t>G | 605呎 (2房)
-$1,483万
-$24,512/呎
-(已定价未售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>A | 946呎 (3房)
-$2,779万
-$29,378/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>B | 753呎 (3房)
-$2,305万
-$30,608/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>C | 942呎 (3房)
-$2,829万
-$30,035/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 564呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 453呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 567呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>朗贤峯第IIA期 - 3座 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>150 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>103 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>19 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>28 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 2405呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 1391呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 1005呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E6" s="17" t="inlineStr"/>
-      <c r="F6" s="17" t="inlineStr"/>
-      <c r="G6" s="17" t="inlineStr"/>
-      <c r="H6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 2362呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 1402呎 (4+房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 991呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="17" t="inlineStr"/>
-      <c r="F7" s="17" t="inlineStr"/>
-      <c r="G7" s="17" t="inlineStr"/>
-      <c r="H7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>A | 988呎 (3房)
-$2,392万
-$24,209/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,217万
-$24,665/呎
-(24年-07月)</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="inlineStr">
-        <is>
-          <t>D | 970呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F8" s="16" t="inlineStr">
-        <is>
-          <t>E | 567呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>F | 924呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H8" s="17" t="inlineStr"/>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>A | 988呎 (3房)
-$2,262万
-$22,898/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,150万
-$23,910/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="inlineStr">
-        <is>
-          <t>D | 970呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F9" s="16" t="inlineStr">
-        <is>
-          <t>E | 567呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G9" s="16" t="inlineStr">
-        <is>
-          <t>F | 924呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H9" s="17" t="inlineStr"/>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,262万
-$22,799/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,140万
-$23,808/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>D | 970呎 (3房)
-$2,542万
-$26,206/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F10" s="16" t="inlineStr">
-        <is>
-          <t>E | 567呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G10" s="18" t="inlineStr">
-        <is>
-          <t>F | 924呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H10" s="17" t="inlineStr"/>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,250万
-$22,682/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,758万
-$24,254/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,128万
-$23,673/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>D | 970呎 (3房)
-$2,520万
-$25,979/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F11" s="16" t="inlineStr">
-        <is>
-          <t>E | 567呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G11" s="18" t="inlineStr">
-        <is>
-          <t>F | 924呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,283万
-$23,018/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,760万
-$24,280/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,161万
-$24,036/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>D | 970呎 (3房)
-$2,492万
-$25,692/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F12" s="16" t="inlineStr">
-        <is>
-          <t>E | 567呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G12" s="19" t="inlineStr">
-        <is>
-          <t>F | 924呎 (3房)
-$2,341万
-$25,333/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,227万
-$22,446/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,783万
-$24,597/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,119万
-$23,566/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>D | 970呎 (3房)
-$2,468万
-$25,438/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="F13" s="16" t="inlineStr">
-        <is>
-          <t>E | 567呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G13" s="18" t="inlineStr">
-        <is>
-          <t>F | 924呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,216万
-$22,335/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,732万
-$23,895/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,097万
-$23,323/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E14" s="18" t="inlineStr">
-        <is>
-          <t>D | 970呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F14" s="16" t="inlineStr">
-        <is>
-          <t>E | 567呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G14" s="18" t="inlineStr">
-        <is>
-          <t>F | 924呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,226万
-$22,435/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,732万
-$23,895/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,107万
-$23,439/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="E15" s="18" t="inlineStr">
-        <is>
-          <t>D | 970呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F15" s="16" t="inlineStr">
-        <is>
-          <t>E | 567呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G15" s="18" t="inlineStr">
-        <is>
-          <t>F | 924呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,238万
-$22,566/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,715万
-$23,658/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,118万
-$23,564/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E16" s="18" t="inlineStr">
-        <is>
-          <t>D | 970呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F16" s="16" t="inlineStr">
-        <is>
-          <t>E | 567呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G16" s="18" t="inlineStr">
-        <is>
-          <t>F | 924呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,237万
-$22,553/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,707万
-$23,541/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,063万
-$22,948/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E17" s="18" t="inlineStr">
-        <is>
-          <t>D | 970呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F17" s="16" t="inlineStr">
-        <is>
-          <t>E | 567呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G17" s="18" t="inlineStr">
-        <is>
-          <t>F | 924呎 (3房)
-暂无价格
-暂无呎价
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,216万
-$22,342/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,709万
-$23,567/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,098万
-$23,336/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>D | 682呎 (2房)
-$1,413万
-$20,713/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F18" s="19" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$1,022万
-$20,859/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="G18" s="19" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$1,032万
-$21,061/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="H18" s="19" t="inlineStr">
-        <is>
-          <t>G | 601呎 (2房)
-$1,231万
-$20,488/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,162万
-$21,794/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,690万
-$23,308/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,045万
-$22,750/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>D | 629呎 (2房)
-$1,300万
-$20,671/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F19" s="19" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$1,020万
-$20,808/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G19" s="19" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$1,029万
-$21,008/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="H19" s="19" t="inlineStr">
-        <is>
-          <t>G | 601呎 (2房)
-$1,228万
-$20,438/呎
-(24年-09月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,194万
-$22,121/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,682万
-$23,193/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,035万
-$22,637/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>D | 629呎 (2房)
-$1,286万
-$20,444/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F20" s="19" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$1,008万
-$20,580/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G20" s="19" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$1,024万
-$20,904/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="H20" s="19" t="inlineStr">
-        <is>
-          <t>G | 601呎 (2房)
-$1,230万
-$20,461/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,183万
-$22,010/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,673万
-$23,077/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,025万
-$22,525/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>D | 629呎 (2房)
-$1,280万
-$20,342/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F21" s="19" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$1,010万
-$20,604/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G21" s="19" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$1,019万
-$20,802/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H21" s="19" t="inlineStr">
-        <is>
-          <t>G | 601呎 (2房)
-$1,216万
-$20,235/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,129万
-$21,463/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,675万
-$23,101/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,017万
-$22,435/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>D | 629呎 (2房)
-$1,281万
-$20,366/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$998万
-$20,378/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="G22" s="19" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$1,008万
-$20,573/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H22" s="19" t="inlineStr">
-        <is>
-          <t>G | 601呎 (2房)
-$1,218万
-$20,258/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,173万
-$21,901/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,675万
-$23,101/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,015万
-$22,413/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>D | 629呎 (2房)
-$1,273万
-$20,242/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="F23" s="19" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$998万
-$20,378/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G23" s="19" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$1,008万
-$20,573/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H23" s="19" t="inlineStr">
-        <is>
-          <t>G | 601呎 (2房)
-$1,218万
-$20,258/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,110万
-$21,266/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,648万
-$22,735/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,036万
-$22,646/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>D | 629呎 (2房)
-$1,261万
-$20,043/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F24" s="19" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$995万
-$20,300/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="G24" s="19" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$998万
-$20,371/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="H24" s="19" t="inlineStr">
-        <is>
-          <t>G | 601呎 (2房)
-$1,198万
-$19,937/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,101万
-$21,180/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,640万
-$22,623/呎
-(24年-09月)</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,026万
-$22,532/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>D | 629呎 (2房)
-$1,242万
-$19,749/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$980万
-$20,002/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="G25" s="19" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$984万
-$20,071/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="H25" s="19" t="inlineStr">
-        <is>
-          <t>G | 601呎 (2房)
-$1,181万
-$19,644/呎
-(24年-11月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>5/F</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,130万
-$21,470/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,642万
-$22,647/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$1,980万
-$22,024/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>D | 629呎 (2房)
-$1,224万
-$19,458/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="F26" s="19" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$960万
-$19,590/呎
-(24年-12月)</t>
-        </is>
-      </c>
-      <c r="G26" s="19" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$975万
-$19,898/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="H26" s="19" t="inlineStr">
-        <is>
-          <t>G | 601呎 (2房)
-$1,170万
-$19,474/呎
-(24年-10月)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,121万
-$21,381/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,624万
-$22,399/呎
-(24年-10月)</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$2,006万
-$22,309/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E27" s="18" t="inlineStr">
-        <is>
-          <t>D | 629呎 (2房)
-$1,471万
-$23,382/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F27" s="18" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$1,153万
-$23,539/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G27" s="18" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$1,164万
-$23,765/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
-        <is>
-          <t>G | 601呎 (2房)
-$1,358万
-$22,596/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="65" customHeight="1">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>2/F</t>
-        </is>
-      </c>
-      <c r="B28" s="19" t="inlineStr">
-        <is>
-          <t>A | 992呎 (3房)
-$2,088万
-$21,048/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="C28" s="19" t="inlineStr">
-        <is>
-          <t>B | 725呎 (3房)
-$1,616万
-$22,288/呎
-(24年-11月)</t>
-        </is>
-      </c>
-      <c r="D28" s="19" t="inlineStr">
-        <is>
-          <t>C | 899呎 (3房)
-$1,996万
-$22,198/呎
-(24年-06月)</t>
-        </is>
-      </c>
-      <c r="E28" s="18" t="inlineStr">
-        <is>
-          <t>D | 629呎 (2房)
-$1,463万
-$23,266/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="F28" s="18" t="inlineStr">
-        <is>
-          <t>E | 490呎 (2房)
-$1,148万
-$23,424/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="G28" s="18" t="inlineStr">
-        <is>
-          <t>F | 490呎 (2房)
-$1,159万
-$23,649/呎
-(暂停销售)</t>
-        </is>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>G | 601呎 (2房)
-$1,351万
-$22,484/呎
-(暂停销售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="65" customHeight="1">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>1/F</t>
-        </is>
-      </c>
-      <c r="B29" s="19" t="inlineStr">
-        <is>
-          <t>A | 948呎 (3房)
-$2,558万
-$26,982/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="C29" s="16" t="inlineStr">
-        <is>
-          <t>B | 684呎 (3房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D29" s="19" t="inlineStr">
-        <is>
-          <t>C | 846呎 (3房)
-$2,359万
-$27,882/呎
-(24年-05月)</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="inlineStr">
-        <is>
-          <t>D | 590呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F29" s="16" t="inlineStr">
-        <is>
-          <t>E | 453呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G29" s="16" t="inlineStr">
-        <is>
-          <t>F | 453呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
-        <is>
-          <t>G | 564呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/九龙-何文田-朗贤峰第IIA期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIA期.xlsx
@@ -8,6 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1座" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2座" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3座" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +22,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +44,101 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +149,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +214,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +230,63 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +663,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -20581,4 +20770,4361 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>1座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2540呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 2299呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr"/>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2473呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 2299呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr"/>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1431呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 1271呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 1333呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F7" s="21" t="inlineStr"/>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1431呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 1271呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="inlineStr">
+        <is>
+          <t>D | 1333呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F8" s="21" t="inlineStr"/>
+      <c r="G8" s="21" t="inlineStr"/>
+      <c r="H8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1433呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>C | 1271呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 1333呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="inlineStr"/>
+      <c r="G9" s="21" t="inlineStr"/>
+      <c r="H9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1433呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>C | 1271呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 1333呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr"/>
+      <c r="G10" s="21" t="inlineStr"/>
+      <c r="H10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>B | 1433呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 1271呎 (4+房)
+$3503万
+$27,563/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 1333呎 (4+房)
+$3681万
+$27,617/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr"/>
+      <c r="G11" s="21" t="inlineStr"/>
+      <c r="H11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 1433呎 (4+房)
+$4133万
+$28,841/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 1271呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 1333呎 (4+房)
+$3645万
+$27,344/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr"/>
+      <c r="G12" s="21" t="inlineStr"/>
+      <c r="H12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1433呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 1271呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 1333呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr"/>
+      <c r="G13" s="21" t="inlineStr"/>
+      <c r="H13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1433呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 1271呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 1333呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr"/>
+      <c r="G14" s="21" t="inlineStr"/>
+      <c r="H14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 1433呎 (4+房)
+$3992万
+$27,856/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 1271呎 (4+房)
+$3377万
+$26,569/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D | 1333呎 (4+房)
+$3468万
+$26,015/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr"/>
+      <c r="G15" s="21" t="inlineStr"/>
+      <c r="H15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 1433呎 (4+房)
+$3932万
+$27,441/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>C | 1271呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D | 1333呎 (4+房)
+$3503万
+$26,281/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr"/>
+      <c r="G16" s="21" t="inlineStr"/>
+      <c r="H16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 998呎 (3房)
+$2477万
+$24,822/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 797呎 (3房)
+$1991万
+$24,979/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>C | 998呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>D | 685呎 (3房)
+$1515万
+$22,118/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>E | 482呎 (2房)
+$1073万
+$22,266/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>F | 482呎 (2房)
+$1061万
+$22,012/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>G | 624呎 (2房)
+$1339万
+$21,452/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 998呎 (3房)
+$2528万
+$25,329/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 797呎 (3房)
+$1986万
+$24,917/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 998呎 (3房)
+$2477万
+$24,818/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 636呎 (2房)
+$1404万
+$22,072/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>E | 482呎 (2房)
+$1071万
+$22,212/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>F | 482呎 (2房)
+$1052万
+$21,824/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t>G | 624呎 (2房)
+$1628万
+$26,096/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 998呎 (3房)
+$2478万
+$24,835/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>B | 797呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>C | 998呎 (3房)
+$2514万
+$25,188/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 636呎 (2房)
+$1397万
+$21,964/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>E | 482呎 (2房)
+$1065万
+$22,102/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>F | 482呎 (2房)
+$1047万
+$21,716/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t>G | 624呎 (2房)
+$1620万
+$25,968/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 998呎 (3房)
+$2446万
+$24,512/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 797呎 (3房)
+$1966万
+$24,670/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>C | 998呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>D | 636呎 (2房)
+$1390万
+$21,855/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>E | 482呎 (2房)
+$1060万
+$21,992/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>F | 482呎 (2房)
+$1042万
+$21,610/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t>G | 624呎 (2房)
+$1612万
+$25,838/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 998呎 (3房)
+$2435万
+$24,397/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 797呎 (3房)
+$1996万
+$25,048/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="D21" s="22" t="inlineStr">
+        <is>
+          <t>C | 998呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>D | 636呎 (2房)
+$1383万
+$21,747/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>E | 482呎 (2房)
+$1055万
+$21,884/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>F | 482呎 (2房)
+$1036万
+$21,502/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H21" s="22" t="inlineStr">
+        <is>
+          <t>G | 624呎 (2房)
+$1604万
+$25,712/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 998呎 (3房)
+$2484万
+$24,888/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 797呎 (3房)
+$1956万
+$24,547/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D22" s="22" t="inlineStr">
+        <is>
+          <t>C | 998呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E22" s="22" t="inlineStr">
+        <is>
+          <t>D | 636呎 (2房)
+$1687万
+$26,520/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F22" s="22" t="inlineStr">
+        <is>
+          <t>E | 482呎 (2房)
+$1286万
+$26,687/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>F | 482呎 (2房)
+$1036万
+$21,502/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H22" s="22" t="inlineStr">
+        <is>
+          <t>G | 624呎 (2房)
+$1604万
+$25,712/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 998呎 (3房)
+$2410万
+$24,149/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C23" s="22" t="inlineStr">
+        <is>
+          <t>B | 797呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D23" s="22" t="inlineStr">
+        <is>
+          <t>C | 998呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E23" s="22" t="inlineStr">
+        <is>
+          <t>D | 636呎 (2房)
+$1670万
+$26,259/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F23" s="22" t="inlineStr">
+        <is>
+          <t>E | 482呎 (2房)
+$1274万
+$26,425/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>F | 482呎 (2房)
+$1026万
+$21,290/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="H23" s="22" t="inlineStr">
+        <is>
+          <t>G | 624呎 (2房)
+$1588万
+$25,457/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 998呎 (3房)
+$2398万
+$24,030/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C24" s="22" t="inlineStr">
+        <is>
+          <t>B | 797呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D24" s="22" t="inlineStr">
+        <is>
+          <t>C | 998呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E24" s="22" t="inlineStr">
+        <is>
+          <t>D | 636呎 (2房)
+$1662万
+$26,129/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F24" s="22" t="inlineStr">
+        <is>
+          <t>E | 482呎 (2房)
+$1267万
+$26,295/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G24" s="22" t="inlineStr">
+        <is>
+          <t>F | 482呎 (2房)
+$1245万
+$25,838/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H24" s="22" t="inlineStr">
+        <is>
+          <t>G | 624呎 (2房)
+$1581万
+$25,332/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 998呎 (3房)
+$2386万
+$23,910/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C25" s="22" t="inlineStr">
+        <is>
+          <t>B | 797呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D25" s="22" t="inlineStr">
+        <is>
+          <t>C | 998呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E25" s="22" t="inlineStr">
+        <is>
+          <t>D | 636呎 (2房)
+$1654万
+$26,002/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F25" s="22" t="inlineStr">
+        <is>
+          <t>E | 482呎 (2房)
+$1261万
+$26,164/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>F | 482呎 (2房)
+$1239万
+$25,707/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H25" s="22" t="inlineStr">
+        <is>
+          <t>G | 624呎 (2房)
+$1573万
+$25,207/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="inlineStr">
+        <is>
+          <t>A | 998呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C26" s="22" t="inlineStr">
+        <is>
+          <t>B | 797呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D26" s="22" t="inlineStr">
+        <is>
+          <t>C | 998呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 636呎 (2房)
+$1646万
+$25,873/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 482呎 (2房)
+$1255万
+$26,035/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 482呎 (2房)
+$1233万
+$25,581/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 624呎 (2房)
+$1565万
+$25,082/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>A | 998呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>B | 797呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D27" s="22" t="inlineStr">
+        <is>
+          <t>C | 998呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 636呎 (2房)
+$1637万
+$25,744/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 482呎 (2房)
+$1249万
+$25,907/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 482呎 (2房)
+$1227万
+$25,456/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>G | 624呎 (2房)
+$1557万
+$24,958/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$2666万
+$28,122/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>B | 754呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D28" s="22" t="inlineStr">
+        <is>
+          <t>C | 947呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 597呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 445呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 585呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>2座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2572呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1252呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 1249呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2492呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1505呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 994呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 1429呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 1431呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 926呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 568呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 968呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G7" s="21" t="inlineStr"/>
+      <c r="H7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>A | 1429呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 1431呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="22" t="inlineStr">
+        <is>
+          <t>C | 926呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 568呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>E | 968呎 (3房)
+$2551万
+$26,352/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="G8" s="21" t="inlineStr"/>
+      <c r="H8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 1431呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>C | 926呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="inlineStr">
+        <is>
+          <t>D | 568呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F9" s="22" t="inlineStr">
+        <is>
+          <t>E | 968呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G9" s="21" t="inlineStr"/>
+      <c r="H9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>B | 1431呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>C | 926呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="inlineStr">
+        <is>
+          <t>D | 568呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F10" s="22" t="inlineStr">
+        <is>
+          <t>E | 968呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G10" s="21" t="inlineStr"/>
+      <c r="H10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+$4048万
+$28,267/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>B | 1431呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 926呎 (3房)
+$2402万
+$25,943/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="inlineStr">
+        <is>
+          <t>D | 568呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F11" s="23" t="inlineStr">
+        <is>
+          <t>E | 968呎 (3房)
+$2530万
+$26,136/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G11" s="21" t="inlineStr"/>
+      <c r="H11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+$4005万
+$27,968/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>B | 1431呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>C | 926呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="inlineStr">
+        <is>
+          <t>D | 568呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F12" s="23" t="inlineStr">
+        <is>
+          <t>E | 968呎 (3房)
+$2452万
+$25,331/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G12" s="21" t="inlineStr"/>
+      <c r="H12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>B | 1431呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>C | 926呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="inlineStr">
+        <is>
+          <t>D | 568呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F13" s="23" t="inlineStr">
+        <is>
+          <t>E | 968呎 (3房)
+$2530万
+$26,133/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G13" s="21" t="inlineStr"/>
+      <c r="H13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>B | 1431呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>C | 926呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="inlineStr">
+        <is>
+          <t>D | 568呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F14" s="23" t="inlineStr">
+        <is>
+          <t>E | 968呎 (3房)
+$2427万
+$25,072/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="inlineStr"/>
+      <c r="H14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+$3828万
+$26,732/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>B | 1431呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>C | 926呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="inlineStr">
+        <is>
+          <t>D | 568呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F15" s="23" t="inlineStr">
+        <is>
+          <t>E | 968呎 (3房)
+$2428万
+$25,087/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="inlineStr"/>
+      <c r="H15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>A | 1432呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>B | 1431呎 (4+房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 926呎 (3房)
+$2268万
+$24,492/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="inlineStr">
+        <is>
+          <t>D | 568呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F16" s="23" t="inlineStr">
+        <is>
+          <t>E | 968呎 (3房)
+$2338万
+$24,153/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="inlineStr"/>
+      <c r="H16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>B | 796呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>C | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="inlineStr">
+        <is>
+          <t>D | 602呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F17" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G17" s="20" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H17" s="20" t="inlineStr">
+        <is>
+          <t>G | 605呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>B | 796呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>C | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="inlineStr">
+        <is>
+          <t>D | 602呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F18" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G18" s="20" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H18" s="20" t="inlineStr">
+        <is>
+          <t>G | 605呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>B | 796呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="inlineStr">
+        <is>
+          <t>C | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="inlineStr">
+        <is>
+          <t>D | 602呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F19" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G19" s="20" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H19" s="20" t="inlineStr">
+        <is>
+          <t>G | 605呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>B | 796呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>C | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="inlineStr">
+        <is>
+          <t>D | 602呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F20" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G20" s="20" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H20" s="20" t="inlineStr">
+        <is>
+          <t>G | 605呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>B | 796呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>C | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="inlineStr">
+        <is>
+          <t>D | 602呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F21" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G21" s="20" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
+        <is>
+          <t>G | 605呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>B | 796呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>C | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="inlineStr">
+        <is>
+          <t>D | 602呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F22" s="20" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
+        <is>
+          <t>G | 605呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>B | 796呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>C | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="inlineStr">
+        <is>
+          <t>D | 602呎 (2房)
+$1521万
+$25,271/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F23" s="24" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$1261万
+$25,733/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G23" s="24" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$1250万
+$25,500/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
+        <is>
+          <t>G | 605呎 (2房)
+$1513万
+$25,003/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>B | 796呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>C | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="inlineStr">
+        <is>
+          <t>D | 602呎 (2房)
+$1514万
+$25,146/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F24" s="24" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$1255万
+$25,604/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G24" s="24" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$1243万
+$25,376/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
+        <is>
+          <t>G | 605呎 (2房)
+$1505万
+$24,879/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>B | 796呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>C | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="inlineStr">
+        <is>
+          <t>D | 602呎 (2房)
+$1463万
+$24,301/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F25" s="24" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$1248万
+$25,478/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G25" s="24" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$1237万
+$25,251/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
+        <is>
+          <t>G | 605呎 (2房)
+$1498万
+$24,757/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>B | 796呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>C | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="inlineStr">
+        <is>
+          <t>D | 602呎 (2房)
+$1456万
+$24,181/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F26" s="24" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$1242万
+$25,353/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G26" s="24" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$1231万
+$25,127/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
+        <is>
+          <t>G | 605呎 (2房)
+$1490万
+$24,635/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>A | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>B | 796呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>C | 997呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="inlineStr">
+        <is>
+          <t>D | 602呎 (2房)
+$1448万
+$24,061/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F27" s="24" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$1236万
+$25,227/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="G27" s="24" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$1225万
+$25,002/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
+        <is>
+          <t>G | 605呎 (2房)
+$1483万
+$24,512/呎
+(已定价未售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>A | 946呎 (3房)
+$2779万
+$29,378/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="C28" s="23" t="inlineStr">
+        <is>
+          <t>B | 753呎 (3房)
+$2305万
+$30,608/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>C | 942呎 (3房)
+$2829万
+$30,035/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 564呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 453呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 567呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>3座 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="H4" s="19" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 2405呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 1391呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 1005呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E5" s="21" t="inlineStr"/>
+      <c r="F5" s="21" t="inlineStr"/>
+      <c r="G5" s="21" t="inlineStr"/>
+      <c r="H5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 2362呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 1402呎 (4+房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 991呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="21" t="inlineStr"/>
+      <c r="F6" s="21" t="inlineStr"/>
+      <c r="G6" s="21" t="inlineStr"/>
+      <c r="H6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B7" s="23" t="inlineStr">
+        <is>
+          <t>A | 988呎 (3房)
+$2392万
+$24,209/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2217万
+$24,665/呎
+(24年-07月)</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="inlineStr">
+        <is>
+          <t>D | 970呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="inlineStr">
+        <is>
+          <t>E | 567呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G7" s="20" t="inlineStr">
+        <is>
+          <t>F | 924呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H7" s="21" t="inlineStr"/>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B8" s="23" t="inlineStr">
+        <is>
+          <t>A | 988呎 (3房)
+$2262万
+$22,898/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D8" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2150万
+$23,910/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="inlineStr">
+        <is>
+          <t>D | 970呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="inlineStr">
+        <is>
+          <t>E | 567呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G8" s="20" t="inlineStr">
+        <is>
+          <t>F | 924呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H8" s="21" t="inlineStr"/>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2262万
+$22,799/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2140万
+$23,808/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 970呎 (3房)
+$2542万
+$26,206/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F9" s="20" t="inlineStr">
+        <is>
+          <t>E | 567呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t>F | 924呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H9" s="21" t="inlineStr"/>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2250万
+$22,682/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1758万
+$24,254/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2128万
+$23,673/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="inlineStr">
+        <is>
+          <t>D | 970呎 (3房)
+$2520万
+$25,979/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="inlineStr">
+        <is>
+          <t>E | 567呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G10" s="22" t="inlineStr">
+        <is>
+          <t>F | 924呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2283万
+$23,018/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1760万
+$24,280/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2161万
+$24,036/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 970呎 (3房)
+$2492万
+$25,692/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F11" s="20" t="inlineStr">
+        <is>
+          <t>E | 567呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G11" s="23" t="inlineStr">
+        <is>
+          <t>F | 924呎 (3房)
+$2341万
+$25,333/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2227万
+$22,446/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1783万
+$24,597/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2119万
+$23,566/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 970呎 (3房)
+$2468万
+$25,438/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="F12" s="20" t="inlineStr">
+        <is>
+          <t>E | 567呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G12" s="22" t="inlineStr">
+        <is>
+          <t>F | 924呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2216万
+$22,335/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1732万
+$23,895/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2097万
+$23,323/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="inlineStr">
+        <is>
+          <t>D | 970呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F13" s="20" t="inlineStr">
+        <is>
+          <t>E | 567呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G13" s="22" t="inlineStr">
+        <is>
+          <t>F | 924呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2226万
+$22,435/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1732万
+$23,895/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2107万
+$23,439/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="inlineStr">
+        <is>
+          <t>D | 970呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F14" s="20" t="inlineStr">
+        <is>
+          <t>E | 567呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G14" s="22" t="inlineStr">
+        <is>
+          <t>F | 924呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2238万
+$22,566/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1715万
+$23,658/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2118万
+$23,564/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E15" s="22" t="inlineStr">
+        <is>
+          <t>D | 970呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F15" s="20" t="inlineStr">
+        <is>
+          <t>E | 567呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G15" s="22" t="inlineStr">
+        <is>
+          <t>F | 924呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2237万
+$22,553/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1707万
+$23,541/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2063万
+$22,948/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E16" s="22" t="inlineStr">
+        <is>
+          <t>D | 970呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F16" s="20" t="inlineStr">
+        <is>
+          <t>E | 567呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G16" s="22" t="inlineStr">
+        <is>
+          <t>F | 924呎 (3房)
+-
+-
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2216万
+$22,342/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1709万
+$23,567/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2098万
+$23,336/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>D | 682呎 (2房)
+$1413万
+$20,713/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F17" s="23" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$1022万
+$20,859/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="G17" s="23" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$1032万
+$21,061/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="H17" s="23" t="inlineStr">
+        <is>
+          <t>G | 601呎 (2房)
+$1231万
+$20,488/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2162万
+$21,794/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1690万
+$23,308/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2045万
+$22,750/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 629呎 (2房)
+$1300万
+$20,671/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F18" s="23" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$1020万
+$20,808/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G18" s="23" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$1029万
+$21,008/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="H18" s="23" t="inlineStr">
+        <is>
+          <t>G | 601呎 (2房)
+$1228万
+$20,438/呎
+(24年-09月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2194万
+$22,121/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1682万
+$23,193/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2035万
+$22,637/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 629呎 (2房)
+$1286万
+$20,444/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F19" s="23" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$1008万
+$20,580/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G19" s="23" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$1024万
+$20,904/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="H19" s="23" t="inlineStr">
+        <is>
+          <t>G | 601呎 (2房)
+$1230万
+$20,461/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2183万
+$22,010/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1673万
+$23,077/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2025万
+$22,525/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>D | 629呎 (2房)
+$1280万
+$20,342/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F20" s="23" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$1010万
+$20,604/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G20" s="23" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$1019万
+$20,802/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H20" s="23" t="inlineStr">
+        <is>
+          <t>G | 601呎 (2房)
+$1216万
+$20,235/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2129万
+$21,463/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1675万
+$23,101/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2017万
+$22,435/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>D | 629呎 (2房)
+$1281万
+$20,366/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="F21" s="23" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$998万
+$20,378/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="G21" s="23" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$1008万
+$20,573/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H21" s="23" t="inlineStr">
+        <is>
+          <t>G | 601呎 (2房)
+$1218万
+$20,258/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2173万
+$21,901/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1675万
+$23,101/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2015万
+$22,413/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>D | 629呎 (2房)
+$1273万
+$20,242/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="F22" s="23" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$998万
+$20,378/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G22" s="23" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$1008万
+$20,573/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H22" s="23" t="inlineStr">
+        <is>
+          <t>G | 601呎 (2房)
+$1218万
+$20,258/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2110万
+$21,266/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1648万
+$22,735/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2036万
+$22,646/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>D | 629呎 (2房)
+$1261万
+$20,043/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F23" s="23" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$995万
+$20,300/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="G23" s="23" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$998万
+$20,371/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="H23" s="23" t="inlineStr">
+        <is>
+          <t>G | 601呎 (2房)
+$1198万
+$19,937/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2101万
+$21,180/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1640万
+$22,623/呎
+(24年-09月)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2026万
+$22,532/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>D | 629呎 (2房)
+$1242万
+$19,749/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F24" s="23" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$980万
+$20,002/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="G24" s="23" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$984万
+$20,071/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="H24" s="23" t="inlineStr">
+        <is>
+          <t>G | 601呎 (2房)
+$1181万
+$19,644/呎
+(24年-11月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2130万
+$21,470/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1642万
+$22,647/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$1980万
+$22,024/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>D | 629呎 (2房)
+$1224万
+$19,458/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F25" s="23" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$960万
+$19,590/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="G25" s="23" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$975万
+$19,898/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="H25" s="23" t="inlineStr">
+        <is>
+          <t>G | 601呎 (2房)
+$1170万
+$19,474/呎
+(24年-10月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2121万
+$21,381/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1624万
+$22,399/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$2006万
+$22,309/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E26" s="22" t="inlineStr">
+        <is>
+          <t>D | 629呎 (2房)
+$1471万
+$23,382/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F26" s="22" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$1153万
+$23,539/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G26" s="22" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$1164万
+$23,765/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H26" s="22" t="inlineStr">
+        <is>
+          <t>G | 601呎 (2房)
+$1358万
+$22,596/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="58" customHeight="1">
+      <c r="A27" s="19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B27" s="23" t="inlineStr">
+        <is>
+          <t>A | 992呎 (3房)
+$2088万
+$21,048/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="C27" s="23" t="inlineStr">
+        <is>
+          <t>B | 725呎 (3房)
+$1616万
+$22,288/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D27" s="23" t="inlineStr">
+        <is>
+          <t>C | 899呎 (3房)
+$1996万
+$22,198/呎
+(24年-06月)</t>
+        </is>
+      </c>
+      <c r="E27" s="22" t="inlineStr">
+        <is>
+          <t>D | 629呎 (2房)
+$1463万
+$23,266/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="F27" s="22" t="inlineStr">
+        <is>
+          <t>E | 490呎 (2房)
+$1148万
+$23,424/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="G27" s="22" t="inlineStr">
+        <is>
+          <t>F | 490呎 (2房)
+$1159万
+$23,649/呎
+(暂停销售)</t>
+        </is>
+      </c>
+      <c r="H27" s="22" t="inlineStr">
+        <is>
+          <t>G | 601呎 (2房)
+$1351万
+$22,484/呎
+(暂停销售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="58" customHeight="1">
+      <c r="A28" s="19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B28" s="23" t="inlineStr">
+        <is>
+          <t>A | 948呎 (3房)
+$2558万
+$26,982/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>B | 684呎 (3房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D28" s="23" t="inlineStr">
+        <is>
+          <t>C | 846呎 (3房)
+$2359万
+$27,882/呎
+(24年-05月)</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="inlineStr">
+        <is>
+          <t>D | 590呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F28" s="20" t="inlineStr">
+        <is>
+          <t>E | 453呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G28" s="20" t="inlineStr">
+        <is>
+          <t>F | 453呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
+        <is>
+          <t>G | 564呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/九龙-何文田-朗贤峰第IIA期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIA期.xlsx
@@ -663,7 +663,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/九龙-何文田-朗贤峰第IIA期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIA期.xlsx
@@ -20643,7 +20643,7 @@
         </is>
       </c>
       <c r="E300" s="4" t="n">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F300" s="3" t="inlineStr">
         <is>
@@ -20659,7 +20659,7 @@
         <v>22501000</v>
       </c>
       <c r="I300" s="5" t="n">
-        <v>22682</v>
+        <v>22705</v>
       </c>
       <c r="J300" s="3" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>22501000</v>
       </c>
       <c r="L300" s="5" t="n">
-        <v>22682</v>
+        <v>22705</v>
       </c>
       <c r="M300" s="3" t="inlineStr">
         <is>
@@ -24297,7 +24297,7 @@
         </is>
       </c>
       <c r="E357" s="4" t="n">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
@@ -24313,7 +24313,7 @@
         <v>21944000</v>
       </c>
       <c r="I357" s="5" t="n">
-        <v>22121</v>
+        <v>22143</v>
       </c>
       <c r="J357" s="3" t="inlineStr">
         <is>
@@ -24324,7 +24324,7 @@
         <v>21944000</v>
       </c>
       <c r="L357" s="5" t="n">
-        <v>22121</v>
+        <v>22143</v>
       </c>
       <c r="M357" s="3" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
           <t>C | 1271呎 (4+房)
 $3503万
 $27,563/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -28683,7 +28683,7 @@
           <t>D | 1333呎 (4+房)
 $3681万
 $27,617/呎
-(24年-06月-11日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -28709,7 +28709,7 @@
           <t>B | 1433呎 (4+房)
 $4133万
 $28,841/呎
-(24年-10月-02日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -28725,7 +28725,7 @@
           <t>D | 1333呎 (4+房)
 $3645万
 $27,344/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -28835,7 +28835,7 @@
           <t>B | 1433呎 (4+房)
 $3992万
 $27,856/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -28843,7 +28843,7 @@
           <t>C | 1271呎 (4+房)
 $3377万
 $26,569/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -28851,7 +28851,7 @@
           <t>D | 1333呎 (4+房)
 $3468万
 $26,015/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr"/>
@@ -28877,7 +28877,7 @@
           <t>B | 1433呎 (4+房)
 $3932万
 $27,441/呎
-(25年-01月-06日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -28893,7 +28893,7 @@
           <t>D | 1333呎 (4+房)
 $3503万
 $26,281/呎
-(24年-06月-10日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -28911,7 +28911,7 @@
           <t>A | 998呎 (3房)
 $2477万
 $24,822/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -28919,7 +28919,7 @@
           <t>B | 797呎 (3房)
 $1991万
 $24,979/呎
-(24年-12月-16日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -28935,7 +28935,7 @@
           <t>D | 685呎 (3房)
 $1515万
 $22,118/呎
-(24年-12月-30日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -28943,7 +28943,7 @@
           <t>E | 482呎 (2房)
 $1073万
 $22,266/呎
-(24年-10月-11日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -28951,7 +28951,7 @@
           <t>F | 482呎 (2房)
 $1061万
 $22,012/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -28959,7 +28959,7 @@
           <t>G | 624呎 (2房)
 $1339万
 $21,452/呎
-(24年-11月-11日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -28974,7 +28974,7 @@
           <t>A | 998呎 (3房)
 $2528万
 $25,329/呎
-(24年-05月-27日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -28982,7 +28982,7 @@
           <t>B | 797呎 (3房)
 $1986万
 $24,917/呎
-(24年-12月-16日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -28990,7 +28990,7 @@
           <t>C | 998呎 (3房)
 $2477万
 $24,818/呎
-(24年-06月-16日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -28998,7 +28998,7 @@
           <t>D | 636呎 (2房)
 $1404万
 $22,072/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -29006,7 +29006,7 @@
           <t>E | 482呎 (2房)
 $1071万
 $22,212/呎
-(24年-10月-29日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -29014,7 +29014,7 @@
           <t>F | 482呎 (2房)
 $1052万
 $21,824/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -29037,7 +29037,7 @@
           <t>A | 998呎 (3房)
 $2478万
 $24,835/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -29053,7 +29053,7 @@
           <t>C | 998呎 (3房)
 $2514万
 $25,188/呎
-(24年-07月-04日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -29061,7 +29061,7 @@
           <t>D | 636呎 (2房)
 $1397万
 $21,964/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -29069,7 +29069,7 @@
           <t>E | 482呎 (2房)
 $1065万
 $22,102/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -29077,7 +29077,7 @@
           <t>F | 482呎 (2房)
 $1047万
 $21,716/呎
-(24年-09月-26日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -29100,7 +29100,7 @@
           <t>A | 998呎 (3房)
 $2446万
 $24,512/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -29108,7 +29108,7 @@
           <t>B | 797呎 (3房)
 $1966万
 $24,670/呎
-(24年-12月-22日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -29124,7 +29124,7 @@
           <t>D | 636呎 (2房)
 $1390万
 $21,855/呎
-(24年-09月-24日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -29132,7 +29132,7 @@
           <t>E | 482呎 (2房)
 $1060万
 $21,992/呎
-(24年-10月-02日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
@@ -29140,7 +29140,7 @@
           <t>F | 482呎 (2房)
 $1042万
 $21,610/呎
-(24年-09月-24日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -29163,7 +29163,7 @@
           <t>A | 998呎 (3房)
 $2435万
 $24,397/呎
-(24年-06月-02日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -29171,7 +29171,7 @@
           <t>B | 797呎 (3房)
 $1996万
 $25,048/呎
-(24年-06月-17日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -29187,7 +29187,7 @@
           <t>D | 636呎 (2房)
 $1383万
 $21,747/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -29195,7 +29195,7 @@
           <t>E | 482呎 (2房)
 $1055万
 $21,884/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -29203,7 +29203,7 @@
           <t>F | 482呎 (2房)
 $1036万
 $21,502/呎
-(24年-11月-12日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -29226,7 +29226,7 @@
           <t>A | 998呎 (3房)
 $2484万
 $24,888/呎
-(24年-06月-17日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -29234,7 +29234,7 @@
           <t>B | 797呎 (3房)
 $1956万
 $24,547/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -29266,7 +29266,7 @@
           <t>F | 482呎 (2房)
 $1036万
 $21,502/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -29289,7 +29289,7 @@
           <t>A | 998呎 (3房)
 $2410万
 $24,149/呎
-(24年-12月-22日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -29329,7 +29329,7 @@
           <t>F | 482呎 (2房)
 $1026万
 $21,290/呎
-(25年-01月-16日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -29352,7 +29352,7 @@
           <t>A | 998呎 (3房)
 $2398万
 $24,030/呎
-(24年-06月-26日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -29415,7 +29415,7 @@
           <t>A | 998呎 (3房)
 $2386万
 $23,910/呎
-(24年-12月-30日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -29604,7 +29604,7 @@
           <t>A | 948呎 (3房)
 $2666万
 $28,122/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -29959,7 +29959,7 @@
           <t>E | 968呎 (3房)
 $2551万
 $26,352/呎
-(24年-07月-21日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr"/>
@@ -30074,7 +30074,7 @@
           <t>A | 1432呎 (4+房)
 $4048万
 $28,267/呎
-(24年-06月-02日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -30090,7 +30090,7 @@
           <t>C | 926呎 (3房)
 $2402万
 $25,943/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -30106,7 +30106,7 @@
           <t>E | 968呎 (3房)
 $2530万
 $26,136/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr"/>
@@ -30123,7 +30123,7 @@
           <t>A | 1432呎 (4+房)
 $4005万
 $27,968/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -30155,7 +30155,7 @@
           <t>E | 968呎 (3房)
 $2452万
 $25,331/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr"/>
@@ -30204,7 +30204,7 @@
           <t>E | 968呎 (3房)
 $2530万
 $26,133/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr"/>
@@ -30253,7 +30253,7 @@
           <t>E | 968呎 (3房)
 $2427万
 $25,072/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr"/>
@@ -30270,7 +30270,7 @@
           <t>A | 1432呎 (4+房)
 $3828万
 $26,732/呎
-(24年-10月-07日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -30302,7 +30302,7 @@
           <t>E | 968呎 (3房)
 $2428万
 $25,087/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr"/>
@@ -30335,7 +30335,7 @@
           <t>C | 926呎 (3房)
 $2268万
 $24,492/呎
-(24年-10月-20日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -30351,7 +30351,7 @@
           <t>E | 968呎 (3房)
 $2338万
 $24,153/呎
-(24年-10月-01日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr"/>
@@ -31061,7 +31061,7 @@
           <t>A | 946呎 (3房)
 $2779万
 $29,378/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -31069,7 +31069,7 @@
           <t>B | 753呎 (3房)
 $2305万
 $30,608/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -31077,7 +31077,7 @@
           <t>C | 942呎 (3房)
 $2829万
 $30,035/呎
-(24年-11月-14日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -31335,7 +31335,7 @@
           <t>A | 988呎 (3房)
 $2392万
 $24,209/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -31351,7 +31351,7 @@
           <t>C | 899呎 (3房)
 $2217万
 $24,665/呎
-(24年-07月-15日)</t>
+(24年-07月)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -31391,7 +31391,7 @@
           <t>A | 988呎 (3房)
 $2262万
 $22,898/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -31407,7 +31407,7 @@
           <t>C | 899呎 (3房)
 $2150万
 $23,910/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -31447,7 +31447,7 @@
           <t>A | 992呎 (3房)
 $2262万
 $22,799/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -31463,7 +31463,7 @@
           <t>C | 899呎 (3房)
 $2140万
 $23,808/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -31471,7 +31471,7 @@
           <t>D | 970呎 (3房)
 $2542万
 $26,206/呎
-(24年-06月-06日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -31500,10 +31500,10 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 991呎 (3房)
 $2250万
-$22,682/呎
-(24年-05月-28日)</t>
+$22,705/呎
+(24年-05月)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -31511,7 +31511,7 @@
           <t>B | 725呎 (3房)
 $1758万
 $24,254/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -31519,7 +31519,7 @@
           <t>C | 899呎 (3房)
 $2128万
 $23,673/呎
-(24年-05月-23日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -31527,7 +31527,7 @@
           <t>D | 970呎 (3房)
 $2520万
 $25,979/呎
-(24年-06月-10日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -31559,7 +31559,7 @@
           <t>A | 992呎 (3房)
 $2283万
 $23,018/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -31567,7 +31567,7 @@
           <t>B | 725呎 (3房)
 $1760万
 $24,280/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -31575,7 +31575,7 @@
           <t>C | 899呎 (3房)
 $2161万
 $24,036/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -31583,7 +31583,7 @@
           <t>D | 970呎 (3房)
 $2492万
 $25,692/呎
-(24年-06月-06日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -31599,7 +31599,7 @@
           <t>F | 924呎 (3房)
 $2341万
 $25,333/呎
-(24年-11月-06日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr"/>
@@ -31615,7 +31615,7 @@
           <t>A | 992呎 (3房)
 $2227万
 $22,446/呎
-(24年-05月-20日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -31623,7 +31623,7 @@
           <t>B | 725呎 (3房)
 $1783万
 $24,597/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -31631,7 +31631,7 @@
           <t>C | 899呎 (3房)
 $2119万
 $23,566/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -31639,7 +31639,7 @@
           <t>D | 970呎 (3房)
 $2468万
 $25,438/呎
-(24年-06月-12日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -31671,7 +31671,7 @@
           <t>A | 992呎 (3房)
 $2216万
 $22,335/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -31679,7 +31679,7 @@
           <t>B | 725呎 (3房)
 $1732万
 $23,895/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -31687,7 +31687,7 @@
           <t>C | 899呎 (3房)
 $2097万
 $23,323/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -31727,7 +31727,7 @@
           <t>A | 992呎 (3房)
 $2226万
 $22,435/呎
-(24年-05月-26日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -31735,7 +31735,7 @@
           <t>B | 725呎 (3房)
 $1732万
 $23,895/呎
-(24年-11月-03日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -31743,7 +31743,7 @@
           <t>C | 899呎 (3房)
 $2107万
 $23,439/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -31783,7 +31783,7 @@
           <t>A | 992呎 (3房)
 $2238万
 $22,566/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -31791,7 +31791,7 @@
           <t>B | 725呎 (3房)
 $1715万
 $23,658/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -31799,7 +31799,7 @@
           <t>C | 899呎 (3房)
 $2118万
 $23,564/呎
-(24年-06月-05日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -31839,7 +31839,7 @@
           <t>A | 992呎 (3房)
 $2237万
 $22,553/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -31847,7 +31847,7 @@
           <t>B | 725呎 (3房)
 $1707万
 $23,541/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -31855,7 +31855,7 @@
           <t>C | 899呎 (3房)
 $2063万
 $22,948/呎
-(24年-06月-11日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -31895,7 +31895,7 @@
           <t>A | 992呎 (3房)
 $2216万
 $22,342/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -31903,7 +31903,7 @@
           <t>B | 725呎 (3房)
 $1709万
 $23,567/呎
-(24年-10月-31日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -31911,7 +31911,7 @@
           <t>C | 899呎 (3房)
 $2098万
 $23,336/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -31919,7 +31919,7 @@
           <t>D | 682呎 (2房)
 $1413万
 $20,713/呎
-(24年-09月-24日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -31927,7 +31927,7 @@
           <t>E | 490呎 (2房)
 $1022万
 $20,859/呎
-(24年-09月-26日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -31935,7 +31935,7 @@
           <t>F | 490呎 (2房)
 $1032万
 $21,061/呎
-(24年-09月-26日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -31943,7 +31943,7 @@
           <t>G | 601呎 (2房)
 $1231万
 $20,488/呎
-(24年-09月-29日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -31958,7 +31958,7 @@
           <t>A | 992呎 (3房)
 $2162万
 $21,794/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -31966,7 +31966,7 @@
           <t>B | 725呎 (3房)
 $1690万
 $23,308/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -31974,7 +31974,7 @@
           <t>C | 899呎 (3房)
 $2045万
 $22,750/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -31982,7 +31982,7 @@
           <t>D | 629呎 (2房)
 $1300万
 $20,671/呎
-(24年-09月-22日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -31990,7 +31990,7 @@
           <t>E | 490呎 (2房)
 $1020万
 $20,808/呎
-(24年-10月-02日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -31998,7 +31998,7 @@
           <t>F | 490呎 (2房)
 $1029万
 $21,008/呎
-(24年-09月-24日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
@@ -32006,7 +32006,7 @@
           <t>G | 601呎 (2房)
 $1228万
 $20,438/呎
-(24年-09月-23日)</t>
+(24年-09月)</t>
         </is>
       </c>
     </row>
@@ -32018,10 +32018,10 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>A | 992呎 (3房)
+          <t>A | 991呎 (3房)
 $2194万
-$22,121/呎
-(24年-05月-16日)</t>
+$22,143/呎
+(24年-05月)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -32029,7 +32029,7 @@
           <t>B | 725呎 (3房)
 $1682万
 $23,193/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -32037,7 +32037,7 @@
           <t>C | 899呎 (3房)
 $2035万
 $22,637/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -32045,7 +32045,7 @@
           <t>D | 629呎 (2房)
 $1286万
 $20,444/呎
-(24年-09月-24日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -32053,7 +32053,7 @@
           <t>E | 490呎 (2房)
 $1008万
 $20,580/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -32061,7 +32061,7 @@
           <t>F | 490呎 (2房)
 $1024万
 $20,904/呎
-(24年-09月-29日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
@@ -32069,7 +32069,7 @@
           <t>G | 601呎 (2房)
 $1230万
 $20,461/呎
-(24年-10月-02日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -32084,7 +32084,7 @@
           <t>A | 992呎 (3房)
 $2183万
 $22,010/呎
-(24年-05月-15日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -32092,7 +32092,7 @@
           <t>B | 725呎 (3房)
 $1673万
 $23,077/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -32100,7 +32100,7 @@
           <t>C | 899呎 (3房)
 $2025万
 $22,525/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -32108,7 +32108,7 @@
           <t>D | 629呎 (2房)
 $1280万
 $20,342/呎
-(24年-09月-24日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -32116,7 +32116,7 @@
           <t>E | 490呎 (2房)
 $1010万
 $20,604/呎
-(24年-10月-22日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
@@ -32124,7 +32124,7 @@
           <t>F | 490呎 (2房)
 $1019万
 $20,802/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
@@ -32132,7 +32132,7 @@
           <t>G | 601呎 (2房)
 $1216万
 $20,235/呎
-(24年-10月-09日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -32147,7 +32147,7 @@
           <t>A | 992呎 (3房)
 $2129万
 $21,463/呎
-(24年-05月-13日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -32155,7 +32155,7 @@
           <t>B | 725呎 (3房)
 $1675万
 $23,101/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -32163,7 +32163,7 @@
           <t>C | 899呎 (3房)
 $2017万
 $22,435/呎
-(24年-05月-21日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -32171,7 +32171,7 @@
           <t>D | 629呎 (2房)
 $1281万
 $20,366/呎
-(24年-09月-24日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -32179,7 +32179,7 @@
           <t>E | 490呎 (2房)
 $998万
 $20,378/呎
-(24年-09月-24日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -32187,7 +32187,7 @@
           <t>F | 490呎 (2房)
 $1008万
 $20,573/呎
-(24年-10月-30日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
@@ -32195,7 +32195,7 @@
           <t>G | 601呎 (2房)
 $1218万
 $20,258/呎
-(24年-10月-20日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -32210,7 +32210,7 @@
           <t>A | 992呎 (3房)
 $2173万
 $21,901/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -32218,7 +32218,7 @@
           <t>B | 725呎 (3房)
 $1675万
 $23,101/呎
-(24年-10月-01日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -32226,7 +32226,7 @@
           <t>C | 899呎 (3房)
 $2015万
 $22,413/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -32234,7 +32234,7 @@
           <t>D | 629呎 (2房)
 $1273万
 $20,242/呎
-(24年-10月-28日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -32242,7 +32242,7 @@
           <t>E | 490呎 (2房)
 $998万
 $20,378/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
@@ -32250,7 +32250,7 @@
           <t>F | 490呎 (2房)
 $1008万
 $20,573/呎
-(24年-10月-08日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
@@ -32258,7 +32258,7 @@
           <t>G | 601呎 (2房)
 $1218万
 $20,258/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -32273,7 +32273,7 @@
           <t>A | 992呎 (3房)
 $2110万
 $21,266/呎
-(24年-05月-28日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -32281,7 +32281,7 @@
           <t>B | 725呎 (3房)
 $1648万
 $22,735/呎
-(24年-10月-01日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -32289,7 +32289,7 @@
           <t>C | 899呎 (3房)
 $2036万
 $22,646/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -32297,7 +32297,7 @@
           <t>D | 629呎 (2房)
 $1261万
 $20,043/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
@@ -32305,7 +32305,7 @@
           <t>E | 490呎 (2房)
 $995万
 $20,300/呎
-(24年-11月-21日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="G23" s="23" t="inlineStr">
@@ -32313,7 +32313,7 @@
           <t>F | 490呎 (2房)
 $998万
 $20,371/呎
-(24年-12月-19日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="H23" s="23" t="inlineStr">
@@ -32321,7 +32321,7 @@
           <t>G | 601呎 (2房)
 $1198万
 $19,937/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -32336,7 +32336,7 @@
           <t>A | 992呎 (3房)
 $2101万
 $21,180/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -32344,7 +32344,7 @@
           <t>B | 725呎 (3房)
 $1640万
 $22,623/呎
-(24年-09月-22日)</t>
+(24年-09月)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -32352,7 +32352,7 @@
           <t>C | 899呎 (3房)
 $2026万
 $22,532/呎
-(24年-05月-16日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -32360,7 +32360,7 @@
           <t>D | 629呎 (2房)
 $1242万
 $19,749/呎
-(24年-11月-13日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -32368,7 +32368,7 @@
           <t>E | 490呎 (2房)
 $980万
 $20,002/呎
-(24年-10月-23日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
@@ -32376,7 +32376,7 @@
           <t>F | 490呎 (2房)
 $984万
 $20,071/呎
-(24年-11月-25日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
@@ -32384,7 +32384,7 @@
           <t>G | 601呎 (2房)
 $1181万
 $19,644/呎
-(24年-11月-07日)</t>
+(24年-11月)</t>
         </is>
       </c>
     </row>
@@ -32399,7 +32399,7 @@
           <t>A | 992呎 (3房)
 $2130万
 $21,470/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -32407,7 +32407,7 @@
           <t>B | 725呎 (3房)
 $1642万
 $22,647/呎
-(24年-10月-01日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -32415,7 +32415,7 @@
           <t>C | 899呎 (3房)
 $1980万
 $22,024/呎
-(24年-05月-29日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -32423,7 +32423,7 @@
           <t>D | 629呎 (2房)
 $1224万
 $19,458/呎
-(24年-11月-27日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -32431,7 +32431,7 @@
           <t>E | 490呎 (2房)
 $960万
 $19,590/呎
-(24年-12月-26日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
@@ -32439,7 +32439,7 @@
           <t>F | 490呎 (2房)
 $975万
 $19,898/呎
-(24年-10月-17日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
@@ -32447,7 +32447,7 @@
           <t>G | 601呎 (2房)
 $1170万
 $19,474/呎
-(24年-10月-02日)</t>
+(24年-10月)</t>
         </is>
       </c>
     </row>
@@ -32462,7 +32462,7 @@
           <t>A | 992呎 (3房)
 $2121万
 $21,381/呎
-(24年-06月-02日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -32470,7 +32470,7 @@
           <t>B | 725呎 (3房)
 $1624万
 $22,399/呎
-(24年-10月-06日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -32478,7 +32478,7 @@
           <t>C | 899呎 (3房)
 $2006万
 $22,309/呎
-(24年-06月-02日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -32525,7 +32525,7 @@
           <t>A | 992呎 (3房)
 $2088万
 $21,048/呎
-(24年-06月-11日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -32533,7 +32533,7 @@
           <t>B | 725呎 (3房)
 $1616万
 $22,288/呎
-(24年-11月-17日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -32541,7 +32541,7 @@
           <t>C | 899呎 (3房)
 $1996万
 $22,198/呎
-(24年-06月-17日)</t>
+(24年-06月)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -32588,7 +32588,7 @@
           <t>A | 948呎 (3房)
 $2558万
 $26,982/呎
-(24年-05月-19日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -32604,7 +32604,7 @@
           <t>C | 846呎 (3房)
 $2359万
 $27,882/呎
-(24年-05月-22日)</t>
+(24年-05月)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">

--- a/files/九龙-何文田-朗贤峰第IIA期.xlsx
+++ b/files/九龙-何文田-朗贤峰第IIA期.xlsx
@@ -28675,7 +28675,7 @@
           <t>C | 1271呎 (4+房)
 $3503万
 $27,563/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -28683,7 +28683,7 @@
           <t>D | 1333呎 (4+房)
 $3681万
 $27,617/呎
-(24年-06月)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -28709,7 +28709,7 @@
           <t>B | 1433呎 (4+房)
 $4133万
 $28,841/呎
-(24年-10月)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -28725,7 +28725,7 @@
           <t>D | 1333呎 (4+房)
 $3645万
 $27,344/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -28835,7 +28835,7 @@
           <t>B | 1433呎 (4+房)
 $3992万
 $27,856/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -28843,7 +28843,7 @@
           <t>C | 1271呎 (4+房)
 $3377万
 $26,569/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -28851,7 +28851,7 @@
           <t>D | 1333呎 (4+房)
 $3468万
 $26,015/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr"/>
@@ -28877,7 +28877,7 @@
           <t>B | 1433呎 (4+房)
 $3932万
 $27,441/呎
-(25年-01月)</t>
+(25年-01月-06日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -28893,7 +28893,7 @@
           <t>D | 1333呎 (4+房)
 $3503万
 $26,281/呎
-(24年-06月)</t>
+(24年-06月-10日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -28911,7 +28911,7 @@
           <t>A | 998呎 (3房)
 $2477万
 $24,822/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -28919,7 +28919,7 @@
           <t>B | 797呎 (3房)
 $1991万
 $24,979/呎
-(24年-12月)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -28935,7 +28935,7 @@
           <t>D | 685呎 (3房)
 $1515万
 $22,118/呎
-(24年-12月)</t>
+(24年-12月-30日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -28943,7 +28943,7 @@
           <t>E | 482呎 (2房)
 $1073万
 $22,266/呎
-(24年-10月)</t>
+(24年-10月-11日)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -28951,7 +28951,7 @@
           <t>F | 482呎 (2房)
 $1061万
 $22,012/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -28959,7 +28959,7 @@
           <t>G | 624呎 (2房)
 $1339万
 $21,452/呎
-(24年-11月)</t>
+(24年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -28974,7 +28974,7 @@
           <t>A | 998呎 (3房)
 $2528万
 $25,329/呎
-(24年-05月)</t>
+(24年-05月-27日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -28982,7 +28982,7 @@
           <t>B | 797呎 (3房)
 $1986万
 $24,917/呎
-(24年-12月)</t>
+(24年-12月-16日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -28990,7 +28990,7 @@
           <t>C | 998呎 (3房)
 $2477万
 $24,818/呎
-(24年-06月)</t>
+(24年-06月-16日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -28998,7 +28998,7 @@
           <t>D | 636呎 (2房)
 $1404万
 $22,072/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -29006,7 +29006,7 @@
           <t>E | 482呎 (2房)
 $1071万
 $22,212/呎
-(24年-10月)</t>
+(24年-10月-29日)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -29014,7 +29014,7 @@
           <t>F | 482呎 (2房)
 $1052万
 $21,824/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -29037,7 +29037,7 @@
           <t>A | 998呎 (3房)
 $2478万
 $24,835/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -29053,7 +29053,7 @@
           <t>C | 998呎 (3房)
 $2514万
 $25,188/呎
-(24年-07月)</t>
+(24年-07月-04日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -29061,7 +29061,7 @@
           <t>D | 636呎 (2房)
 $1397万
 $21,964/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -29069,7 +29069,7 @@
           <t>E | 482呎 (2房)
 $1065万
 $22,102/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -29077,7 +29077,7 @@
           <t>F | 482呎 (2房)
 $1047万
 $21,716/呎
-(24年-09月)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -29100,7 +29100,7 @@
           <t>A | 998呎 (3房)
 $2446万
 $24,512/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -29108,7 +29108,7 @@
           <t>B | 797呎 (3房)
 $1966万
 $24,670/呎
-(24年-12月)</t>
+(24年-12月-22日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -29124,7 +29124,7 @@
           <t>D | 636呎 (2房)
 $1390万
 $21,855/呎
-(24年-09月)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -29132,7 +29132,7 @@
           <t>E | 482呎 (2房)
 $1060万
 $21,992/呎
-(24年-10月)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
@@ -29140,7 +29140,7 @@
           <t>F | 482呎 (2房)
 $1042万
 $21,610/呎
-(24年-09月)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="H20" s="22" t="inlineStr">
@@ -29163,7 +29163,7 @@
           <t>A | 998呎 (3房)
 $2435万
 $24,397/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -29171,7 +29171,7 @@
           <t>B | 797呎 (3房)
 $1996万
 $25,048/呎
-(24年-06月)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -29187,7 +29187,7 @@
           <t>D | 636呎 (2房)
 $1383万
 $21,747/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -29195,7 +29195,7 @@
           <t>E | 482呎 (2房)
 $1055万
 $21,884/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -29203,7 +29203,7 @@
           <t>F | 482呎 (2房)
 $1036万
 $21,502/呎
-(24年-11月)</t>
+(24年-11月-12日)</t>
         </is>
       </c>
       <c r="H21" s="22" t="inlineStr">
@@ -29226,7 +29226,7 @@
           <t>A | 998呎 (3房)
 $2484万
 $24,888/呎
-(24年-06月)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -29234,7 +29234,7 @@
           <t>B | 797呎 (3房)
 $1956万
 $24,547/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -29266,7 +29266,7 @@
           <t>F | 482呎 (2房)
 $1036万
 $21,502/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="H22" s="22" t="inlineStr">
@@ -29289,7 +29289,7 @@
           <t>A | 998呎 (3房)
 $2410万
 $24,149/呎
-(24年-12月)</t>
+(24年-12月-22日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -29329,7 +29329,7 @@
           <t>F | 482呎 (2房)
 $1026万
 $21,290/呎
-(25年-01月)</t>
+(25年-01月-16日)</t>
         </is>
       </c>
       <c r="H23" s="22" t="inlineStr">
@@ -29352,7 +29352,7 @@
           <t>A | 998呎 (3房)
 $2398万
 $24,030/呎
-(24年-06月)</t>
+(24年-06月-26日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -29415,7 +29415,7 @@
           <t>A | 998呎 (3房)
 $2386万
 $23,910/呎
-(24年-12月)</t>
+(24年-12月-30日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -29604,7 +29604,7 @@
           <t>A | 948呎 (3房)
 $2666万
 $28,122/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="C28" s="22" t="inlineStr">
@@ -29959,7 +29959,7 @@
           <t>E | 968呎 (3房)
 $2551万
 $26,352/呎
-(24年-07月)</t>
+(24年-07月-21日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr"/>
@@ -30074,7 +30074,7 @@
           <t>A | 1432呎 (4+房)
 $4048万
 $28,267/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -30090,7 +30090,7 @@
           <t>C | 926呎 (3房)
 $2402万
 $25,943/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E11" s="20" t="inlineStr">
@@ -30106,7 +30106,7 @@
           <t>E | 968呎 (3房)
 $2530万
 $26,136/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr"/>
@@ -30123,7 +30123,7 @@
           <t>A | 1432呎 (4+房)
 $4005万
 $27,968/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -30155,7 +30155,7 @@
           <t>E | 968呎 (3房)
 $2452万
 $25,331/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr"/>
@@ -30204,7 +30204,7 @@
           <t>E | 968呎 (3房)
 $2530万
 $26,133/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr"/>
@@ -30253,7 +30253,7 @@
           <t>E | 968呎 (3房)
 $2427万
 $25,072/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="G14" s="21" t="inlineStr"/>
@@ -30270,7 +30270,7 @@
           <t>A | 1432呎 (4+房)
 $3828万
 $26,732/呎
-(24年-10月)</t>
+(24年-10月-07日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -30302,7 +30302,7 @@
           <t>E | 968呎 (3房)
 $2428万
 $25,087/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr"/>
@@ -30335,7 +30335,7 @@
           <t>C | 926呎 (3房)
 $2268万
 $24,492/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
       <c r="E16" s="20" t="inlineStr">
@@ -30351,7 +30351,7 @@
           <t>E | 968呎 (3房)
 $2338万
 $24,153/呎
-(24年-10月)</t>
+(24年-10月-01日)</t>
         </is>
       </c>
       <c r="G16" s="21" t="inlineStr"/>
@@ -31061,7 +31061,7 @@
           <t>A | 946呎 (3房)
 $2779万
 $29,378/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="C28" s="23" t="inlineStr">
@@ -31069,7 +31069,7 @@
           <t>B | 753呎 (3房)
 $2305万
 $30,608/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="D28" s="23" t="inlineStr">
@@ -31077,7 +31077,7 @@
           <t>C | 942呎 (3房)
 $2829万
 $30,035/呎
-(24年-11月)</t>
+(24年-11月-14日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
@@ -31335,7 +31335,7 @@
           <t>A | 988呎 (3房)
 $2392万
 $24,209/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -31351,7 +31351,7 @@
           <t>C | 899呎 (3房)
 $2217万
 $24,665/呎
-(24年-07月)</t>
+(24年-07月-15日)</t>
         </is>
       </c>
       <c r="E7" s="20" t="inlineStr">
@@ -31391,7 +31391,7 @@
           <t>A | 988呎 (3房)
 $2262万
 $22,898/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -31407,7 +31407,7 @@
           <t>C | 899呎 (3房)
 $2150万
 $23,910/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E8" s="20" t="inlineStr">
@@ -31447,7 +31447,7 @@
           <t>A | 992呎 (3房)
 $2262万
 $22,799/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -31463,7 +31463,7 @@
           <t>C | 899呎 (3房)
 $2140万
 $23,808/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E9" s="23" t="inlineStr">
@@ -31471,7 +31471,7 @@
           <t>D | 970呎 (3房)
 $2542万
 $26,206/呎
-(24年-06月)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="F9" s="20" t="inlineStr">
@@ -31503,7 +31503,7 @@
           <t>A | 991呎 (3房)
 $2250万
 $22,705/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -31511,7 +31511,7 @@
           <t>B | 725呎 (3房)
 $1758万
 $24,254/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -31519,7 +31519,7 @@
           <t>C | 899呎 (3房)
 $2128万
 $23,673/呎
-(24年-05月)</t>
+(24年-05月-23日)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -31527,7 +31527,7 @@
           <t>D | 970呎 (3房)
 $2520万
 $25,979/呎
-(24年-06月)</t>
+(24年-06月-10日)</t>
         </is>
       </c>
       <c r="F10" s="20" t="inlineStr">
@@ -31559,7 +31559,7 @@
           <t>A | 992呎 (3房)
 $2283万
 $23,018/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -31567,7 +31567,7 @@
           <t>B | 725呎 (3房)
 $1760万
 $24,280/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -31575,7 +31575,7 @@
           <t>C | 899呎 (3房)
 $2161万
 $24,036/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -31583,7 +31583,7 @@
           <t>D | 970呎 (3房)
 $2492万
 $25,692/呎
-(24年-06月)</t>
+(24年-06月-06日)</t>
         </is>
       </c>
       <c r="F11" s="20" t="inlineStr">
@@ -31599,7 +31599,7 @@
           <t>F | 924呎 (3房)
 $2341万
 $25,333/呎
-(24年-11月)</t>
+(24年-11月-06日)</t>
         </is>
       </c>
       <c r="H11" s="21" t="inlineStr"/>
@@ -31615,7 +31615,7 @@
           <t>A | 992呎 (3房)
 $2227万
 $22,446/呎
-(24年-05月)</t>
+(24年-05月-20日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -31623,7 +31623,7 @@
           <t>B | 725呎 (3房)
 $1783万
 $24,597/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -31631,7 +31631,7 @@
           <t>C | 899呎 (3房)
 $2119万
 $23,566/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -31639,7 +31639,7 @@
           <t>D | 970呎 (3房)
 $2468万
 $25,438/呎
-(24年-06月)</t>
+(24年-06月-12日)</t>
         </is>
       </c>
       <c r="F12" s="20" t="inlineStr">
@@ -31671,7 +31671,7 @@
           <t>A | 992呎 (3房)
 $2216万
 $22,335/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -31679,7 +31679,7 @@
           <t>B | 725呎 (3房)
 $1732万
 $23,895/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -31687,7 +31687,7 @@
           <t>C | 899呎 (3房)
 $2097万
 $23,323/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -31727,7 +31727,7 @@
           <t>A | 992呎 (3房)
 $2226万
 $22,435/呎
-(24年-05月)</t>
+(24年-05月-26日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -31735,7 +31735,7 @@
           <t>B | 725呎 (3房)
 $1732万
 $23,895/呎
-(24年-11月)</t>
+(24年-11月-03日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -31743,7 +31743,7 @@
           <t>C | 899呎 (3房)
 $2107万
 $23,439/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -31783,7 +31783,7 @@
           <t>A | 992呎 (3房)
 $2238万
 $22,566/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -31791,7 +31791,7 @@
           <t>B | 725呎 (3房)
 $1715万
 $23,658/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -31799,7 +31799,7 @@
           <t>C | 899呎 (3房)
 $2118万
 $23,564/呎
-(24年-06月)</t>
+(24年-06月-05日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -31839,7 +31839,7 @@
           <t>A | 992呎 (3房)
 $2237万
 $22,553/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -31847,7 +31847,7 @@
           <t>B | 725呎 (3房)
 $1707万
 $23,541/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -31855,7 +31855,7 @@
           <t>C | 899呎 (3房)
 $2063万
 $22,948/呎
-(24年-06月)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -31895,7 +31895,7 @@
           <t>A | 992呎 (3房)
 $2216万
 $22,342/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -31903,7 +31903,7 @@
           <t>B | 725呎 (3房)
 $1709万
 $23,567/呎
-(24年-10月)</t>
+(24年-10月-31日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -31911,7 +31911,7 @@
           <t>C | 899呎 (3房)
 $2098万
 $23,336/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -31919,7 +31919,7 @@
           <t>D | 682呎 (2房)
 $1413万
 $20,713/呎
-(24年-09月)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="F17" s="23" t="inlineStr">
@@ -31927,7 +31927,7 @@
           <t>E | 490呎 (2房)
 $1022万
 $20,859/呎
-(24年-09月)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
       <c r="G17" s="23" t="inlineStr">
@@ -31935,7 +31935,7 @@
           <t>F | 490呎 (2房)
 $1032万
 $21,061/呎
-(24年-09月)</t>
+(24年-09月-26日)</t>
         </is>
       </c>
       <c r="H17" s="23" t="inlineStr">
@@ -31943,7 +31943,7 @@
           <t>G | 601呎 (2房)
 $1231万
 $20,488/呎
-(24年-09月)</t>
+(24年-09月-29日)</t>
         </is>
       </c>
     </row>
@@ -31958,7 +31958,7 @@
           <t>A | 992呎 (3房)
 $2162万
 $21,794/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -31966,7 +31966,7 @@
           <t>B | 725呎 (3房)
 $1690万
 $23,308/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -31974,7 +31974,7 @@
           <t>C | 899呎 (3房)
 $2045万
 $22,750/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -31982,7 +31982,7 @@
           <t>D | 629呎 (2房)
 $1300万
 $20,671/呎
-(24年-09月)</t>
+(24年-09月-22日)</t>
         </is>
       </c>
       <c r="F18" s="23" t="inlineStr">
@@ -31990,7 +31990,7 @@
           <t>E | 490呎 (2房)
 $1020万
 $20,808/呎
-(24年-10月)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
       <c r="G18" s="23" t="inlineStr">
@@ -31998,7 +31998,7 @@
           <t>F | 490呎 (2房)
 $1029万
 $21,008/呎
-(24年-09月)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="H18" s="23" t="inlineStr">
@@ -32006,7 +32006,7 @@
           <t>G | 601呎 (2房)
 $1228万
 $20,438/呎
-(24年-09月)</t>
+(24年-09月-23日)</t>
         </is>
       </c>
     </row>
@@ -32021,7 +32021,7 @@
           <t>A | 991呎 (3房)
 $2194万
 $22,143/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -32029,7 +32029,7 @@
           <t>B | 725呎 (3房)
 $1682万
 $23,193/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -32037,7 +32037,7 @@
           <t>C | 899呎 (3房)
 $2035万
 $22,637/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -32045,7 +32045,7 @@
           <t>D | 629呎 (2房)
 $1286万
 $20,444/呎
-(24年-09月)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="F19" s="23" t="inlineStr">
@@ -32053,7 +32053,7 @@
           <t>E | 490呎 (2房)
 $1008万
 $20,580/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="G19" s="23" t="inlineStr">
@@ -32061,7 +32061,7 @@
           <t>F | 490呎 (2房)
 $1024万
 $20,904/呎
-(24年-09月)</t>
+(24年-09月-29日)</t>
         </is>
       </c>
       <c r="H19" s="23" t="inlineStr">
@@ -32069,7 +32069,7 @@
           <t>G | 601呎 (2房)
 $1230万
 $20,461/呎
-(24年-10月)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -32084,7 +32084,7 @@
           <t>A | 992呎 (3房)
 $2183万
 $22,010/呎
-(24年-05月)</t>
+(24年-05月-15日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -32092,7 +32092,7 @@
           <t>B | 725呎 (3房)
 $1673万
 $23,077/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -32100,7 +32100,7 @@
           <t>C | 899呎 (3房)
 $2025万
 $22,525/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -32108,7 +32108,7 @@
           <t>D | 629呎 (2房)
 $1280万
 $20,342/呎
-(24年-09月)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="F20" s="23" t="inlineStr">
@@ -32116,7 +32116,7 @@
           <t>E | 490呎 (2房)
 $1010万
 $20,604/呎
-(24年-10月)</t>
+(24年-10月-22日)</t>
         </is>
       </c>
       <c r="G20" s="23" t="inlineStr">
@@ -32124,7 +32124,7 @@
           <t>F | 490呎 (2房)
 $1019万
 $20,802/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="H20" s="23" t="inlineStr">
@@ -32132,7 +32132,7 @@
           <t>G | 601呎 (2房)
 $1216万
 $20,235/呎
-(24年-10月)</t>
+(24年-10月-09日)</t>
         </is>
       </c>
     </row>
@@ -32147,7 +32147,7 @@
           <t>A | 992呎 (3房)
 $2129万
 $21,463/呎
-(24年-05月)</t>
+(24年-05月-13日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -32155,7 +32155,7 @@
           <t>B | 725呎 (3房)
 $1675万
 $23,101/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -32163,7 +32163,7 @@
           <t>C | 899呎 (3房)
 $2017万
 $22,435/呎
-(24年-05月)</t>
+(24年-05月-21日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -32171,7 +32171,7 @@
           <t>D | 629呎 (2房)
 $1281万
 $20,366/呎
-(24年-09月)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="F21" s="23" t="inlineStr">
@@ -32179,7 +32179,7 @@
           <t>E | 490呎 (2房)
 $998万
 $20,378/呎
-(24年-09月)</t>
+(24年-09月-24日)</t>
         </is>
       </c>
       <c r="G21" s="23" t="inlineStr">
@@ -32187,7 +32187,7 @@
           <t>F | 490呎 (2房)
 $1008万
 $20,573/呎
-(24年-10月)</t>
+(24年-10月-30日)</t>
         </is>
       </c>
       <c r="H21" s="23" t="inlineStr">
@@ -32195,7 +32195,7 @@
           <t>G | 601呎 (2房)
 $1218万
 $20,258/呎
-(24年-10月)</t>
+(24年-10月-20日)</t>
         </is>
       </c>
     </row>
@@ -32210,7 +32210,7 @@
           <t>A | 992呎 (3房)
 $2173万
 $21,901/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -32218,7 +32218,7 @@
           <t>B | 725呎 (3房)
 $1675万
 $23,101/呎
-(24年-10月)</t>
+(24年-10月-01日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -32226,7 +32226,7 @@
           <t>C | 899呎 (3房)
 $2015万
 $22,413/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -32234,7 +32234,7 @@
           <t>D | 629呎 (2房)
 $1273万
 $20,242/呎
-(24年-10月)</t>
+(24年-10月-28日)</t>
         </is>
       </c>
       <c r="F22" s="23" t="inlineStr">
@@ -32242,7 +32242,7 @@
           <t>E | 490呎 (2房)
 $998万
 $20,378/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="G22" s="23" t="inlineStr">
@@ -32250,7 +32250,7 @@
           <t>F | 490呎 (2房)
 $1008万
 $20,573/呎
-(24年-10月)</t>
+(24年-10月-08日)</t>
         </is>
       </c>
       <c r="H22" s="23" t="inlineStr">
@@ -32258,7 +32258,7 @@
           <t>G | 601呎 (2房)
 $1218万
 $20,258/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
     </row>
@@ -32273,7 +32273,7 @@
           <t>A | 992呎 (3房)
 $2110万
 $21,266/呎
-(24年-05月)</t>
+(24年-05月-28日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -32281,7 +32281,7 @@
           <t>B | 725呎 (3房)
 $1648万
 $22,735/呎
-(24年-10月)</t>
+(24年-10月-01日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -32289,7 +32289,7 @@
           <t>C | 899呎 (3房)
 $2036万
 $22,646/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -32297,7 +32297,7 @@
           <t>D | 629呎 (2房)
 $1261万
 $20,043/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
       <c r="F23" s="23" t="inlineStr">
@@ -32305,7 +32305,7 @@
           <t>E | 490呎 (2房)
 $995万
 $20,300/呎
-(24年-11月)</t>
+(24年-11月-21日)</t>
         </is>
       </c>
       <c r="G23" s="23" t="inlineStr">
@@ -32313,7 +32313,7 @@
           <t>F | 490呎 (2房)
 $998万
 $20,371/呎
-(24年-12月)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="H23" s="23" t="inlineStr">
@@ -32321,7 +32321,7 @@
           <t>G | 601呎 (2房)
 $1198万
 $19,937/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
     </row>
@@ -32336,7 +32336,7 @@
           <t>A | 992呎 (3房)
 $2101万
 $21,180/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -32344,7 +32344,7 @@
           <t>B | 725呎 (3房)
 $1640万
 $22,623/呎
-(24年-09月)</t>
+(24年-09月-22日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -32352,7 +32352,7 @@
           <t>C | 899呎 (3房)
 $2026万
 $22,532/呎
-(24年-05月)</t>
+(24年-05月-16日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -32360,7 +32360,7 @@
           <t>D | 629呎 (2房)
 $1242万
 $19,749/呎
-(24年-11月)</t>
+(24年-11月-13日)</t>
         </is>
       </c>
       <c r="F24" s="23" t="inlineStr">
@@ -32368,7 +32368,7 @@
           <t>E | 490呎 (2房)
 $980万
 $20,002/呎
-(24年-10月)</t>
+(24年-10月-23日)</t>
         </is>
       </c>
       <c r="G24" s="23" t="inlineStr">
@@ -32376,7 +32376,7 @@
           <t>F | 490呎 (2房)
 $984万
 $20,071/呎
-(24年-11月)</t>
+(24年-11月-25日)</t>
         </is>
       </c>
       <c r="H24" s="23" t="inlineStr">
@@ -32384,7 +32384,7 @@
           <t>G | 601呎 (2房)
 $1181万
 $19,644/呎
-(24年-11月)</t>
+(24年-11月-07日)</t>
         </is>
       </c>
     </row>
@@ -32399,7 +32399,7 @@
           <t>A | 992呎 (3房)
 $2130万
 $21,470/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -32407,7 +32407,7 @@
           <t>B | 725呎 (3房)
 $1642万
 $22,647/呎
-(24年-10月)</t>
+(24年-10月-01日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -32415,7 +32415,7 @@
           <t>C | 899呎 (3房)
 $1980万
 $22,024/呎
-(24年-05月)</t>
+(24年-05月-29日)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -32423,7 +32423,7 @@
           <t>D | 629呎 (2房)
 $1224万
 $19,458/呎
-(24年-11月)</t>
+(24年-11月-27日)</t>
         </is>
       </c>
       <c r="F25" s="23" t="inlineStr">
@@ -32431,7 +32431,7 @@
           <t>E | 490呎 (2房)
 $960万
 $19,590/呎
-(24年-12月)</t>
+(24年-12月-26日)</t>
         </is>
       </c>
       <c r="G25" s="23" t="inlineStr">
@@ -32439,7 +32439,7 @@
           <t>F | 490呎 (2房)
 $975万
 $19,898/呎
-(24年-10月)</t>
+(24年-10月-17日)</t>
         </is>
       </c>
       <c r="H25" s="23" t="inlineStr">
@@ -32447,7 +32447,7 @@
           <t>G | 601呎 (2房)
 $1170万
 $19,474/呎
-(24年-10月)</t>
+(24年-10月-02日)</t>
         </is>
       </c>
     </row>
@@ -32462,7 +32462,7 @@
           <t>A | 992呎 (3房)
 $2121万
 $21,381/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -32470,7 +32470,7 @@
           <t>B | 725呎 (3房)
 $1624万
 $22,399/呎
-(24年-10月)</t>
+(24年-10月-06日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -32478,7 +32478,7 @@
           <t>C | 899呎 (3房)
 $2006万
 $22,309/呎
-(24年-06月)</t>
+(24年-06月-02日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -32525,7 +32525,7 @@
           <t>A | 992呎 (3房)
 $2088万
 $21,048/呎
-(24年-06月)</t>
+(24年-06月-11日)</t>
         </is>
       </c>
       <c r="C27" s="23" t="inlineStr">
@@ -32533,7 +32533,7 @@
           <t>B | 725呎 (3房)
 $1616万
 $22,288/呎
-(24年-11月)</t>
+(24年-11月-17日)</t>
         </is>
       </c>
       <c r="D27" s="23" t="inlineStr">
@@ -32541,7 +32541,7 @@
           <t>C | 899呎 (3房)
 $1996万
 $22,198/呎
-(24年-06月)</t>
+(24年-06月-17日)</t>
         </is>
       </c>
       <c r="E27" s="22" t="inlineStr">
@@ -32588,7 +32588,7 @@
           <t>A | 948呎 (3房)
 $2558万
 $26,982/呎
-(24年-05月)</t>
+(24年-05月-19日)</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -32604,7 +32604,7 @@
           <t>C | 846呎 (3房)
 $2359万
 $27,882/呎
-(24年-05月)</t>
+(24年-05月-22日)</t>
         </is>
       </c>
       <c r="E28" s="20" t="inlineStr">
